--- a/Cashflow.xlsx
+++ b/Cashflow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkrag\Desktop\Tobias\Privat\Bødekassen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C02D55-16E0-487E-B473-A9ED76931E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CDDDE6-F73E-444A-8D66-0B85C864E9CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-51720" yWindow="-3930" windowWidth="51840" windowHeight="21120" xr2:uid="{C2923B8C-6A8B-4D62-998B-C8D90AD68523}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="106">
   <si>
     <t>Dato</t>
   </si>
@@ -246,9 +246,6 @@
   </si>
   <si>
     <t>Indtægt: EM 2024</t>
-  </si>
-  <si>
-    <t>EM</t>
   </si>
   <si>
     <t>Indtægt: Efterår 2024 - Runde 1 + 2</t>
@@ -1915,7 +1912,7 @@
         <v>62</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="D67" s="5">
         <v>1900</v>
@@ -1929,7 +1926,7 @@
         <v>45530</v>
       </c>
       <c r="B68" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>6</v>
@@ -1946,7 +1943,7 @@
         <v>45538</v>
       </c>
       <c r="B69" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>15</v>
@@ -1963,7 +1960,7 @@
         <v>45550</v>
       </c>
       <c r="B70" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>6</v>
@@ -1980,7 +1977,7 @@
         <v>45573</v>
       </c>
       <c r="B71" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>6</v>
@@ -2014,7 +2011,7 @@
         <v>45623</v>
       </c>
       <c r="B73" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>6</v>
@@ -2031,7 +2028,7 @@
         <v>45639</v>
       </c>
       <c r="B74" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>6</v>
@@ -2048,7 +2045,7 @@
         <v>45644</v>
       </c>
       <c r="B75" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>6</v>
@@ -2065,7 +2062,7 @@
         <v>45651</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>9</v>
@@ -2082,7 +2079,7 @@
         <v>45652</v>
       </c>
       <c r="B77" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>6</v>
@@ -2099,7 +2096,7 @@
         <v>45652</v>
       </c>
       <c r="B78" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>15</v>
@@ -2116,7 +2113,7 @@
         <v>45654</v>
       </c>
       <c r="B79" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>6</v>
@@ -2133,7 +2130,7 @@
         <v>45657</v>
       </c>
       <c r="B80" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>23</v>
@@ -2150,7 +2147,7 @@
         <v>45657</v>
       </c>
       <c r="B81" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>9</v>
@@ -2184,7 +2181,7 @@
         <v>45659</v>
       </c>
       <c r="B83" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>23</v>
@@ -2201,7 +2198,7 @@
         <v>45659</v>
       </c>
       <c r="B84" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>23</v>
@@ -2235,7 +2232,7 @@
         <v>45659</v>
       </c>
       <c r="B86" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>23</v>
@@ -2322,7 +2319,7 @@
         <v>45697</v>
       </c>
       <c r="B91" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>23</v>
@@ -2390,7 +2387,7 @@
         <v>45736</v>
       </c>
       <c r="B95" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>6</v>
@@ -2407,7 +2404,7 @@
         <v>45712</v>
       </c>
       <c r="B96" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>23</v>
@@ -2424,7 +2421,7 @@
         <v>45756</v>
       </c>
       <c r="B97" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>6</v>
@@ -2441,7 +2438,7 @@
         <v>45762</v>
       </c>
       <c r="B98" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>6</v>
@@ -2458,7 +2455,7 @@
         <v>45762</v>
       </c>
       <c r="B99" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>15</v>
@@ -2475,7 +2472,7 @@
         <v>45787</v>
       </c>
       <c r="B100" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>6</v>
@@ -2492,7 +2489,7 @@
         <v>45790</v>
       </c>
       <c r="B101" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>6</v>
@@ -2509,7 +2506,7 @@
         <v>45805</v>
       </c>
       <c r="B102" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>6</v>
@@ -2526,7 +2523,7 @@
         <v>45818</v>
       </c>
       <c r="B103" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>15</v>
@@ -2543,7 +2540,7 @@
         <v>45818</v>
       </c>
       <c r="B104" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>6</v>
@@ -2577,7 +2574,7 @@
         <v>45890</v>
       </c>
       <c r="B106" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>6</v>
@@ -2611,7 +2608,7 @@
         <v>45901</v>
       </c>
       <c r="B108" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>6</v>
@@ -2628,7 +2625,7 @@
         <v>45904</v>
       </c>
       <c r="B109" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>23</v>
@@ -2645,7 +2642,7 @@
         <v>45904</v>
       </c>
       <c r="B110" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>23</v>
@@ -2662,7 +2659,7 @@
         <v>45904</v>
       </c>
       <c r="B111" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>15</v>
@@ -2679,7 +2676,7 @@
         <v>45916</v>
       </c>
       <c r="B112" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>6</v>
@@ -2713,7 +2710,7 @@
         <v>45923</v>
       </c>
       <c r="B114" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>15</v>
@@ -2747,7 +2744,7 @@
         <v>45965</v>
       </c>
       <c r="B116" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>6</v>
@@ -2781,7 +2778,7 @@
         <v>45993</v>
       </c>
       <c r="B118" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>6</v>
@@ -2798,7 +2795,7 @@
         <v>46000</v>
       </c>
       <c r="B119" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C119" s="3" t="s">
         <v>6</v>
@@ -2832,7 +2829,7 @@
         <v>46014</v>
       </c>
       <c r="B121" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>6</v>
@@ -2849,7 +2846,7 @@
         <v>46016</v>
       </c>
       <c r="B122" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>23</v>
@@ -2866,7 +2863,7 @@
         <v>46016</v>
       </c>
       <c r="B123" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>23</v>
@@ -2883,7 +2880,7 @@
         <v>46022</v>
       </c>
       <c r="B124" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>9</v>
@@ -2900,7 +2897,7 @@
         <v>46014</v>
       </c>
       <c r="B125" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>6</v>
@@ -2917,7 +2914,7 @@
         <v>46023</v>
       </c>
       <c r="B126" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>6</v>
@@ -2934,7 +2931,7 @@
         <v>46033</v>
       </c>
       <c r="B127" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C127" s="3" t="s">
         <v>6</v>
@@ -2968,7 +2965,7 @@
         <v>46058</v>
       </c>
       <c r="B129" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>6</v>
@@ -3019,7 +3016,7 @@
         <v>46091</v>
       </c>
       <c r="B132" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>6</v>
@@ -3036,7 +3033,7 @@
         <v>46126</v>
       </c>
       <c r="B133" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>6</v>
@@ -3053,7 +3050,7 @@
         <v>46126</v>
       </c>
       <c r="B134" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>15</v>
@@ -3087,7 +3084,7 @@
         <v>46167</v>
       </c>
       <c r="B136" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>6</v>
@@ -3104,7 +3101,7 @@
         <v>46183</v>
       </c>
       <c r="B137" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>15</v>
@@ -3121,7 +3118,7 @@
         <v>46183</v>
       </c>
       <c r="B138" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>23</v>

--- a/Cashflow.xlsx
+++ b/Cashflow.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkrag\Desktop\Tobias\Privat\Bødekassen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkrag\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CDDDE6-F73E-444A-8D66-0B85C864E9CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AC02838-6852-477D-8A46-74F62DBEA325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51720" yWindow="-3930" windowWidth="51840" windowHeight="21120" xr2:uid="{C2923B8C-6A8B-4D62-998B-C8D90AD68523}"/>
+    <workbookView xWindow="43815" yWindow="4620" windowWidth="19185" windowHeight="11265" xr2:uid="{C2923B8C-6A8B-4D62-998B-C8D90AD68523}"/>
   </bookViews>
   <sheets>
     <sheet name="Cashflow" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="107">
   <si>
     <t>Dato</t>
   </si>
@@ -375,6 +375,9 @@
   </si>
   <si>
     <t>Udgift: Bødekassearrangement (Rob fødselsdag)</t>
+  </si>
+  <si>
+    <t>Indtægt: VM</t>
   </si>
 </sst>
 </file>
@@ -769,7 +772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF965C0C-4D2F-406F-901E-BFD360CE5959}">
-  <dimension ref="A1:I138"/>
+  <dimension ref="A1:I139"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" style="3" customWidth="1"/>
@@ -3130,6 +3133,23 @@
         <v>8</v>
       </c>
     </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A139" s="2">
+        <v>46231</v>
+      </c>
+      <c r="B139" t="s">
+        <v>106</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D139" s="5">
+        <v>1450</v>
+      </c>
+      <c r="E139">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E74" xr:uid="{EC9E4794-C69A-8447-AB43-82CDA37E364A}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Cashflow.xlsx
+++ b/Cashflow.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkrag\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AC02838-6852-477D-8A46-74F62DBEA325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{602E914A-B71E-4E4B-8F56-3AD08CB2E6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43815" yWindow="4620" windowWidth="19185" windowHeight="11265" xr2:uid="{C2923B8C-6A8B-4D62-998B-C8D90AD68523}"/>
+    <workbookView xWindow="41220" yWindow="3420" windowWidth="15945" windowHeight="15690" xr2:uid="{C2923B8C-6A8B-4D62-998B-C8D90AD68523}"/>
   </bookViews>
   <sheets>
     <sheet name="Cashflow" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="108">
   <si>
     <t>Dato</t>
   </si>
@@ -378,6 +378,9 @@
   </si>
   <si>
     <t>Indtægt: VM</t>
+  </si>
+  <si>
+    <t>Indtægt: Bødekassetur - Mallorca (Hus) - Returnering</t>
   </si>
 </sst>
 </file>
@@ -772,7 +775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF965C0C-4D2F-406F-901E-BFD360CE5959}">
-  <dimension ref="A1:I139"/>
+  <dimension ref="A1:I140"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" style="3" customWidth="1"/>
@@ -3150,6 +3153,23 @@
         <v>8</v>
       </c>
     </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A140" s="2">
+        <v>46239</v>
+      </c>
+      <c r="B140" t="s">
+        <v>107</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D140" s="5">
+        <v>7000</v>
+      </c>
+      <c r="E140">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E74" xr:uid="{EC9E4794-C69A-8447-AB43-82CDA37E364A}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Cashflow.xlsx
+++ b/Cashflow.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkrag\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkrag\Desktop\Tobias\Privat\Bødekassen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{602E914A-B71E-4E4B-8F56-3AD08CB2E6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB66316D-12C2-4BA2-8B2B-F4B81B93EFEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41220" yWindow="3420" windowWidth="15945" windowHeight="15690" xr2:uid="{C2923B8C-6A8B-4D62-998B-C8D90AD68523}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cashflow" sheetId="1" r:id="rId1"/>
@@ -21,9 +21,6 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -35,15 +32,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="108">
   <si>
     <t>Dato</t>
   </si>
@@ -51,21 +45,7 @@
     <t>Begivenhed</t>
   </si>
   <si>
-    <r>
-      <t>Katego</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ri</t>
-    </r>
+    <t>Kategori</t>
   </si>
   <si>
     <t>Beløb</t>
@@ -391,7 +371,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -408,15 +388,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -443,7 +414,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -774,8 +745,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF965C0C-4D2F-406F-901E-BFD360CE5959}">
-  <dimension ref="A1:I140"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I142"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" style="3" customWidth="1"/>
@@ -3170,8 +3141,42 @@
         <v>8</v>
       </c>
     </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A141" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B141" t="s">
+        <v>33</v>
+      </c>
+      <c r="C141" t="s">
+        <v>6</v>
+      </c>
+      <c r="D141" s="5">
+        <v>725</v>
+      </c>
+      <c r="E141">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A142" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B142" t="s">
+        <v>87</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D142" s="5">
+        <v>300</v>
+      </c>
+      <c r="E142">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E74" xr:uid="{EC9E4794-C69A-8447-AB43-82CDA37E364A}"/>
+  <autoFilter ref="A1:E74" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Cashflow.xlsx
+++ b/Cashflow.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkrag\Desktop\Tobias\Privat\Bødekassen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB66316D-12C2-4BA2-8B2B-F4B81B93EFEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E3C6FB-456F-45A0-9A60-61834D0C3822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="720" yWindow="720" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cashflow" sheetId="1" r:id="rId1"/>
@@ -3169,7 +3169,7 @@
         <v>6</v>
       </c>
       <c r="D142" s="5">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="E142">
         <v>9</v>

--- a/Cashflow.xlsx
+++ b/Cashflow.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkrag\Desktop\Tobias\Privat\Bødekassen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E3C6FB-456F-45A0-9A60-61834D0C3822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{606A6F54-72CD-4A70-A277-EA391AFE1317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="720" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-51720" yWindow="-3930" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cashflow" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="108">
   <si>
     <t>Dato</t>
   </si>
@@ -746,7 +746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I142"/>
+  <dimension ref="A1:I144"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" style="3" customWidth="1"/>
@@ -3169,9 +3169,43 @@
         <v>6</v>
       </c>
       <c r="D142" s="5">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="E142">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A143" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B143" t="s">
+        <v>37</v>
+      </c>
+      <c r="C143" t="s">
+        <v>6</v>
+      </c>
+      <c r="D143" s="5">
+        <v>725</v>
+      </c>
+      <c r="E143">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A144" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B144" t="s">
+        <v>64</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D144" s="5">
+        <v>-1300</v>
+      </c>
+      <c r="E144">
         <v>9</v>
       </c>
     </row>

--- a/Cashflow.xlsx
+++ b/Cashflow.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkrag\Desktop\Tobias\Privat\Bødekassen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{606A6F54-72CD-4A70-A277-EA391AFE1317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB957E0-6992-460B-ABF0-6413B6662D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51720" yWindow="-3930" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cashflow" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="108">
   <si>
     <t>Dato</t>
   </si>
@@ -746,7 +746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I144"/>
+  <dimension ref="A1:I145"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" style="3" customWidth="1"/>
@@ -3209,6 +3209,23 @@
         <v>9</v>
       </c>
     </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A145" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B145" t="s">
+        <v>88</v>
+      </c>
+      <c r="C145" t="s">
+        <v>6</v>
+      </c>
+      <c r="D145" s="5">
+        <v>675</v>
+      </c>
+      <c r="E145">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E74" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Cashflow.xlsx
+++ b/Cashflow.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkrag\Desktop\Tobias\Privat\Bødekassen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB957E0-6992-460B-ABF0-6413B6662D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A21D70C-683D-4DFC-9806-ACF5CA8EDC44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="109">
   <si>
     <t>Dato</t>
   </si>
@@ -361,6 +361,9 @@
   </si>
   <si>
     <t>Indtægt: Bødekassetur - Mallorca (Hus) - Returnering</t>
+  </si>
+  <si>
+    <t>Udgift: Gave til Frande (30 års)</t>
   </si>
 </sst>
 </file>
@@ -746,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I145"/>
+  <dimension ref="A1:I146"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" style="3" customWidth="1"/>
@@ -3211,18 +3214,35 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B145" t="s">
+        <v>108</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D145" s="5">
+        <v>-1510</v>
+      </c>
+      <c r="E145">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A146" s="2">
         <v>46273</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B146" t="s">
         <v>88</v>
       </c>
-      <c r="C145" t="s">
-        <v>6</v>
-      </c>
-      <c r="D145" s="5">
+      <c r="C146" t="s">
+        <v>6</v>
+      </c>
+      <c r="D146" s="5">
         <v>675</v>
       </c>
-      <c r="E145">
+      <c r="E146">
         <v>9</v>
       </c>
     </row>
